--- a/loss-time/outputs/Loss_time_S32_05-10_den_24-10.xlsx
+++ b/loss-time/outputs/Loss_time_S32_05-10_den_24-10.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Ghi chú review" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'S32 5-10 đến 24-10'!$A$2:$R$56</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'S32 5-10 đến 24-10'!$A$2:$R$57</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="226">
   <si>
     <t xml:space="preserve">LOSS TIME MÃ S32 (OTHER SUPPORT OF PRODUCTION) - 05/10 ĐẾN 24/10/2026 - LÀM RIÊNG, KHÔNG LẪN MÃ KHÁC</t>
   </si>
@@ -389,6 +389,15 @@
     <t xml:space="preserve">Charge to: HÀNG BẢNG MÀU</t>
   </si>
   <si>
+    <t xml:space="preserve">RH12-4706-0423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sửa hàng hộc kéo (veneer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hàng hộc kéo, 4 người cả ngày</t>
+  </si>
+  <si>
     <t xml:space="preserve">AR15-1016-892</t>
   </si>
   <si>
@@ -413,13 +422,7 @@
     <t xml:space="preserve">code 239 (130 m2)</t>
   </si>
   <si>
-    <t xml:space="preserve">RH12-4706-0423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sửa hàng hộc kéo (veneer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thứ Bảy 24/10 8:00-20:00 (có thể là giờ dự kiến)</t>
+    <t xml:space="preserve">Hàng hộc kéo, 2 người</t>
   </si>
   <si>
     <t xml:space="preserve">Tổng</t>
@@ -668,7 +671,7 @@
     <t xml:space="preserve">1. Bảng này CHỈ chứa mã S32, tách hoàn toàn khỏi bảng P20/P26/P22/A2 (không lẫn mã khác). Khi bạn cập nhật, tôi giữ nguyên nguyên tắc này.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Nguồn: 5 file trong gói zip (lấy bản mới nhất mỗi loại: Beam saw bản 24/10, UV bản (1), Ép nóng bản (1), Veneer bản 24/10, file sửa hàng MAC Mr.Hiệp) và 3 hình (thợ sơn tuần 42, cào cước 16/10, bắn cát 15/10). Chỉ lấy dòng từ 05/10 đến 24/10. UV (báo cáo ngày đến 11/10, phát sinh đến 13/10) và Ép nóng (đến 6/10) chưa có số liệu mới.</t>
+    <t xml:space="preserve">2. Nguồn: 5 file trong gói zip (lấy bản mới nhất mỗi loại: Beam saw bản 24/10, UV bản (1), Ép nóng bản (1), Veneer bản mới nhất 24/10, file sửa hàng MAC Mr.Hiệp) và 3 hình (thợ sơn tuần 42, cào cước 16/10, bắn cát 15/10). Chỉ lấy dòng từ 05/10 đến 24/10. UV (báo cáo ngày đến 11/10, phát sinh đến 13/10) và Ép nóng (đến 6/10) chưa có số liệu mới.</t>
   </si>
   <si>
     <t xml:space="preserve">3. Tất cả giờ công trong bảng khớp với số giờ trong nguồn (sheet "Đối chiếu nguồn"). Tổng giờ công xem sheet "Đối chiếu nguồn".</t>
@@ -701,7 +704,7 @@
     <t xml:space="preserve">12. File sửa hàng MAC (Mr.Hiệp) là nguồn mới: 14/10 (AR1069F1233, chạy nhỏ lại mộng, 2 người, 9:00-10:00) và 23/10 (AR15-1016-892, khoan lại lỗ vít 11mm, 2 người, 9:32-11:20). Khu vực Machining, bộ phận ME (cột "Hỗ trợ sửa"). Dòng 23/10: cột tổng thời gian ghi 1:55 nhưng 9:32-11:20 là 1:48, bảng lấy theo giờ bắt đầu - kết thúc (3,6 giờ công) nên sheet Đối chiếu nguồn lệch 0,23 giờ (tô vàng).</t>
   </si>
   <si>
-    <t xml:space="preserve">13. Veneer 24/10 (Thứ Bảy): soạn hàng veneer lỗi trả lại kho (2 người 8:00-9:30, 3 giờ, ME) và sửa hàng hộc kéo RH12-4706-0423 (4 người 8:00-20:00, 48 giờ, ME). Dòng 48 giờ có thể là giờ dự kiến (tô vàng).</t>
+    <t xml:space="preserve">13. Veneer 23/10 và 24/10: sửa hàng hộc kéo RH12-4706-0423: 23/10 4 người 8:00-20:00 (48 giờ, ME; bản trước ghi nhầm ngày 24/10, bản mới đã đổi sang 23/10) và 24/10 2 người 8:00-15:00 (14 giờ, ME, thêm mới). Veneer 24/10 còn dòng soạn hàng veneer lỗi trả lại kho (2 người 8:00-9:30, 3 giờ, ME).</t>
   </si>
   <si>
     <t xml:space="preserve">14. Beam saw 22/10: 7 dòng "HÀNG BẢNG MÀU" (W0114F08, W0276F03, W1981F1055, W2629F1222, W0164F01 x2, W2446F1200) chưa có giờ bắt đầu/kết thúc trong nguồn nên chưa đưa vào bảng (0 giờ). Cần hỏi giờ nếu muốn nhập. Hàng bảng màu theo tiền lệ ghi bộ phận TECHNICAL FINISHING.</t>
@@ -1395,7 +1398,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -4144,240 +4147,295 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="13" t="str">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B53,21)</f>
         <v>W43</v>
       </c>
-      <c r="B53" s="14" t="n">
+      <c r="B53" s="4" t="n">
         <v>46318</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13" t="n">
-        <v>65</v>
-      </c>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H53" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I53" s="15" t="s">
+      <c r="D53" s="3"/>
+      <c r="E53" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J53" s="13" t="s">
+      <c r="J53" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="K53" s="15" t="s">
+      <c r="K53" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="L53" s="15" t="s">
+      <c r="L53" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="M53" s="16" t="n">
-        <v>0.397222222222222</v>
-      </c>
-      <c r="N53" s="16" t="n">
-        <v>0.472222222222222</v>
-      </c>
-      <c r="O53" s="17" t="n">
+      <c r="M53" s="6" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N53" s="6" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="O53" s="7" t="n">
         <f aca="false">(N53-M53)*24</f>
-        <v>1.8</v>
-      </c>
-      <c r="P53" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q53" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q53" s="7" t="n">
         <f aca="false">P53*O53</f>
-        <v>3.6</v>
-      </c>
-      <c r="R53" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8" t="str">
+        <v>48</v>
+      </c>
+      <c r="R53" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="13" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B54,21)</f>
         <v>W43</v>
       </c>
-      <c r="B54" s="9" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C54" s="10" t="s">
+      <c r="B54" s="14" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C54" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H54" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I54" s="10" t="s">
+      <c r="D54" s="13"/>
+      <c r="E54" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I54" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="J54" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K54" s="10" t="s">
+      <c r="J54" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="K54" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="L54" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="M54" s="11" t="n">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="N54" s="11" t="n">
-        <v>0.420833333333333</v>
-      </c>
-      <c r="O54" s="12" t="n">
+      <c r="L54" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="M54" s="16" t="n">
+        <v>0.397222222222222</v>
+      </c>
+      <c r="N54" s="16" t="n">
+        <v>0.472222222222222</v>
+      </c>
+      <c r="O54" s="17" t="n">
         <f aca="false">(N54-M54)*24</f>
-        <v>0.1</v>
-      </c>
-      <c r="P54" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P54" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q54" s="17" t="n">
         <f aca="false">P54*O54</f>
-        <v>0.3</v>
-      </c>
-      <c r="R54" s="8" t="s">
-        <v>41</v>
+        <v>3.6</v>
+      </c>
+      <c r="R54" s="13" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="str">
+      <c r="A55" s="8" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B55,21)</f>
         <v>W43</v>
       </c>
-      <c r="B55" s="4" t="n">
+      <c r="B55" s="9" t="n">
         <v>46319</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55" s="5" t="s">
+      <c r="C55" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I55" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J55" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="K55" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="L55" s="5" t="s">
+      <c r="J55" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K55" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="M55" s="6" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>0.395833333333333</v>
-      </c>
-      <c r="O55" s="7" t="n">
+      <c r="L55" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="M55" s="11" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="N55" s="11" t="n">
+        <v>0.420833333333333</v>
+      </c>
+      <c r="O55" s="12" t="n">
         <f aca="false">(N55-M55)*24</f>
-        <v>1.5</v>
-      </c>
-      <c r="P55" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q55" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P55" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="12" t="n">
         <f aca="false">P55*O55</f>
-        <v>3</v>
-      </c>
-      <c r="R55" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="13" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="R55" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B56,21)</f>
         <v>W43</v>
       </c>
-      <c r="B56" s="14" t="n">
+      <c r="B56" s="4" t="n">
         <v>46319</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H56" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I56" s="15" t="s">
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I56" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J56" s="13" t="s">
+      <c r="J56" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="K56" s="15" t="s">
+      <c r="K56" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="L56" s="15" t="s">
+      <c r="L56" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="M56" s="16" t="n">
+      <c r="M56" s="6" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="N56" s="16" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="O56" s="17" t="n">
+      <c r="N56" s="6" t="n">
+        <v>0.395833333333333</v>
+      </c>
+      <c r="O56" s="7" t="n">
         <f aca="false">(N56-M56)*24</f>
-        <v>12</v>
-      </c>
-      <c r="P56" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q56" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q56" s="7" t="n">
         <f aca="false">P56*O56</f>
-        <v>48</v>
-      </c>
-      <c r="R56" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="R56" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P57" s="18" t="s">
+      <c r="A57" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B57,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="L57" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="Q57" s="19" t="n">
-        <f aca="false">SUM(Q3:Q56)</f>
-        <v>1826.33333333333</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="20" t="s">
+      <c r="M57" s="6" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O57" s="7" t="n">
+        <f aca="false">(N57-M57)*24</f>
+        <v>7</v>
+      </c>
+      <c r="P57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q57" s="7" t="n">
+        <f aca="false">P57*O57</f>
+        <v>14</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P58" s="18" t="s">
         <v>131</v>
       </c>
+      <c r="Q58" s="19" t="n">
+        <f aca="false">SUM(Q3:Q57)</f>
+        <v>1840.33333333333</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="20" t="s">
+        <v>132</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R56"/>
+  <autoFilter ref="A2:R57"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4405,18 +4463,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>26</v>
@@ -4446,7 +4504,7 @@
         <v>85</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4454,46 +4512,46 @@
         <v>46300</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C4" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A4,21)</f>
         <v>W41</v>
       </c>
       <c r="D4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A4,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>46</v>
       </c>
       <c r="E4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A4,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>120</v>
       </c>
       <c r="F4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A4,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0</v>
       </c>
       <c r="G4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A4,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0</v>
       </c>
       <c r="H4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A4,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A4,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A4,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>0</v>
       </c>
       <c r="K4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A4,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A4,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M4" s="24" t="n">
@@ -4506,46 +4564,46 @@
         <v>46301</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C5" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A5,21)</f>
         <v>W41</v>
       </c>
       <c r="D5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A5,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>55</v>
       </c>
       <c r="E5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A5,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>120</v>
       </c>
       <c r="F5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A5,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0</v>
       </c>
       <c r="G5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A5,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0</v>
       </c>
       <c r="H5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A5,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A5,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A5,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>0</v>
       </c>
       <c r="K5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A5,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A5,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M5" s="24" t="n">
@@ -4558,46 +4616,46 @@
         <v>46302</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C6" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A6,21)</f>
         <v>W41</v>
       </c>
       <c r="D6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A6,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A6,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>112</v>
       </c>
       <c r="F6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A6,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0</v>
       </c>
       <c r="G6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A6,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0</v>
       </c>
       <c r="H6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A6,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A6,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A6,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>0</v>
       </c>
       <c r="K6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A6,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A6,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M6" s="24" t="n">
@@ -4610,46 +4668,46 @@
         <v>46303</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C7" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A7,21)</f>
         <v>W41</v>
       </c>
       <c r="D7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A7,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A7,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>104</v>
       </c>
       <c r="F7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A7,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0.2</v>
       </c>
       <c r="G7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A7,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0</v>
       </c>
       <c r="H7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A7,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A7,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A7,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>0</v>
       </c>
       <c r="K7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A7,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A7,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M7" s="24" t="n">
@@ -4662,46 +4720,46 @@
         <v>46304</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C8" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A8,21)</f>
         <v>W41</v>
       </c>
       <c r="D8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A8,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A8,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>132</v>
       </c>
       <c r="F8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A8,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0.6</v>
       </c>
       <c r="G8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A8,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0</v>
       </c>
       <c r="H8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A8,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A8,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A8,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>0</v>
       </c>
       <c r="K8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A8,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A8,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M8" s="24" t="n">
@@ -4714,46 +4772,46 @@
         <v>46305</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C9" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A9,21)</f>
         <v>W41</v>
       </c>
       <c r="D9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A9,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A9,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>116</v>
       </c>
       <c r="F9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A9,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0</v>
       </c>
       <c r="G9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A9,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>3</v>
       </c>
       <c r="H9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A9,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A9,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A9,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>0</v>
       </c>
       <c r="K9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A9,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A9,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M9" s="24" t="n">
@@ -4766,46 +4824,46 @@
         <v>46306</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C10" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A10,21)</f>
         <v>W41</v>
       </c>
       <c r="D10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A10,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A10,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>72</v>
       </c>
       <c r="F10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A10,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0</v>
       </c>
       <c r="G10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A10,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0</v>
       </c>
       <c r="H10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A10,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A10,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A10,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>0</v>
       </c>
       <c r="K10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A10,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A10,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M10" s="24" t="n">
@@ -4818,46 +4876,46 @@
         <v>46307</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C11" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A11,21)</f>
         <v>W42</v>
       </c>
       <c r="D11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A11,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A11,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>0</v>
       </c>
       <c r="F11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A11,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0</v>
       </c>
       <c r="G11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A11,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0</v>
       </c>
       <c r="H11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A11,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A11,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>18</v>
       </c>
       <c r="J11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A11,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>144</v>
       </c>
       <c r="K11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A11,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A11,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M11" s="24" t="n">
@@ -4870,46 +4928,46 @@
         <v>46308</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C12" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A12,21)</f>
         <v>W42</v>
       </c>
       <c r="D12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A12,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A12,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>0</v>
       </c>
       <c r="F12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A12,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0</v>
       </c>
       <c r="G12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A12,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0</v>
       </c>
       <c r="H12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A12,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A12,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>4.5</v>
       </c>
       <c r="J12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A12,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>144</v>
       </c>
       <c r="K12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A12,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A12,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M12" s="24" t="n">
@@ -4922,46 +4980,46 @@
         <v>46309</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A13,21)</f>
         <v>W42</v>
       </c>
       <c r="D13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A13,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A13,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>0</v>
       </c>
       <c r="F13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A13,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0</v>
       </c>
       <c r="G13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A13,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0</v>
       </c>
       <c r="H13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A13,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>2</v>
       </c>
       <c r="I13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A13,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A13,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>144</v>
       </c>
       <c r="K13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A13,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A13,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M13" s="24" t="n">
@@ -4974,46 +5032,46 @@
         <v>46310</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A14,21)</f>
         <v>W42</v>
       </c>
       <c r="D14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A14,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A14,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>0</v>
       </c>
       <c r="F14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A14,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0</v>
       </c>
       <c r="G14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A14,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0.333333333333333</v>
       </c>
       <c r="H14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A14,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A14,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A14,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>144</v>
       </c>
       <c r="K14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A14,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A14,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>32</v>
       </c>
       <c r="M14" s="24" t="n">
@@ -5026,46 +5084,46 @@
         <v>46311</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C15" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A15,21)</f>
         <v>W42</v>
       </c>
       <c r="D15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A15,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A15,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>0</v>
       </c>
       <c r="F15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A15,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0.75</v>
       </c>
       <c r="G15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A15,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0</v>
       </c>
       <c r="H15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A15,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A15,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A15,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>144</v>
       </c>
       <c r="K15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A15,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>9</v>
       </c>
       <c r="L15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A15,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M15" s="24" t="n">
@@ -5078,46 +5136,46 @@
         <v>46312</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C16" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A16,21)</f>
         <v>W42</v>
       </c>
       <c r="D16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A16,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A16,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>0</v>
       </c>
       <c r="F16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A16,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0.2</v>
       </c>
       <c r="G16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A16,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0</v>
       </c>
       <c r="H16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A16,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A16,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A16,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>96</v>
       </c>
       <c r="K16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A16,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A16,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M16" s="24" t="n">
@@ -5130,46 +5188,46 @@
         <v>46314</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C17" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A17,21)</f>
         <v>W43</v>
       </c>
       <c r="D17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A17,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A17,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>0</v>
       </c>
       <c r="F17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A17,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0.35</v>
       </c>
       <c r="G17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A17,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0</v>
       </c>
       <c r="H17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A17,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A17,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A17,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>0</v>
       </c>
       <c r="K17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A17,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A17,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M17" s="24" t="n">
@@ -5182,46 +5240,46 @@
         <v>46315</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A18,21)</f>
         <v>W43</v>
       </c>
       <c r="D18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A18,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A18,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>0</v>
       </c>
       <c r="F18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A18,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0.4</v>
       </c>
       <c r="G18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A18,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>4</v>
       </c>
       <c r="H18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A18,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A18,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A18,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>0</v>
       </c>
       <c r="K18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A18,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A18,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M18" s="24" t="n">
@@ -5234,46 +5292,46 @@
         <v>46317</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C19" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A19,21)</f>
         <v>W43</v>
       </c>
       <c r="D19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A19,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A19,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>0</v>
       </c>
       <c r="F19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A19,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>3.1</v>
       </c>
       <c r="G19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A19,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
         <v>0</v>
       </c>
       <c r="H19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A19,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A19,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A19,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>0</v>
       </c>
       <c r="K19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A19,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A19,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M19" s="24" t="n">
@@ -5286,51 +5344,51 @@
         <v>46318</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A20,21)</f>
         <v>W43</v>
       </c>
       <c r="D20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A20,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A20,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>0</v>
       </c>
       <c r="F20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A20,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0</v>
       </c>
       <c r="G20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A20,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <v>48</v>
       </c>
       <c r="H20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A20,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>3.6</v>
       </c>
       <c r="I20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A20,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A20,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>0</v>
       </c>
       <c r="K20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A20,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A20,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M20" s="24" t="n">
         <f aca="false">SUM(D20:L20)</f>
-        <v>3.6</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5338,56 +5396,56 @@
         <v>46319</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A21,21)</f>
         <v>W43</v>
       </c>
       <c r="D21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A21,'S32 5-10 đến 24-10'!$R$3:$R$56,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
         <v>0</v>
       </c>
       <c r="E21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A21,'S32 5-10 đến 24-10'!$R$3:$R$56,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
         <v>0</v>
       </c>
       <c r="F21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A21,'S32 5-10 đến 24-10'!$R$3:$R$56,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
         <v>0.3</v>
       </c>
       <c r="G21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A21,'S32 5-10 đến 24-10'!$R$3:$R$56,G$3)</f>
-        <v>51</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <v>17</v>
       </c>
       <c r="H21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A21,'S32 5-10 đến 24-10'!$R$3:$R$56,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
         <v>0</v>
       </c>
       <c r="I21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A21,'S32 5-10 đến 24-10'!$R$3:$R$56,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
         <v>0</v>
       </c>
       <c r="J21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A21,'S32 5-10 đến 24-10'!$R$3:$R$56,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
         <v>0</v>
       </c>
       <c r="K21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A21,'S32 5-10 đến 24-10'!$R$3:$R$56,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
         <v>0</v>
       </c>
       <c r="L21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$B$3:$B$56,$A21,'S32 5-10 đến 24-10'!$R$3:$R$56,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
         <v>0</v>
       </c>
       <c r="M21" s="24" t="n">
         <f aca="false">SUM(D21:L21)</f>
-        <v>51.3</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B22" s="25"/>
       <c r="C22" s="25"/>
@@ -5405,7 +5463,7 @@
       </c>
       <c r="G22" s="24" t="n">
         <f aca="false">SUM(G4:G21)</f>
-        <v>58.3333333333333</v>
+        <v>72.3333333333333</v>
       </c>
       <c r="H22" s="24" t="n">
         <f aca="false">SUM(H4:H21)</f>
@@ -5429,47 +5487,47 @@
       </c>
       <c r="M22" s="24" t="n">
         <f aca="false">SUM(M4:M21)</f>
-        <v>1826.33333333333</v>
+        <v>1840.33333333333</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B26" s="27" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$A$3:$A$56,A26)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$A$3:$A$57,A26)</f>
         <v>880.8</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B27" s="27" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$A$3:$A$56,A27)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$A$3:$A$57,A27)</f>
         <v>882.783333333333</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B28" s="27" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$A$3:$A$56,A28)</f>
-        <v>62.75</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$A$3:$A$57,A28)</f>
+        <v>76.75</v>
       </c>
     </row>
   </sheetData>
@@ -5488,7 +5546,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -5506,19 +5564,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>13</v>
@@ -5527,19 +5585,19 @@
         <v>14</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J1" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K1" s="28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L1" s="28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7358,149 +7416,149 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="40" t="n">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="29" t="n">
         <v>46318</v>
       </c>
-      <c r="B52" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="C52" s="42" t="s">
+      <c r="B52" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="D52" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="E52" s="41" t="s">
+      <c r="D52" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="F52" s="43" t="n">
-        <v>0.397222222222222</v>
-      </c>
-      <c r="G52" s="43" t="n">
-        <v>0.472222222222222</v>
-      </c>
-      <c r="H52" s="41" t="n">
-        <v>2</v>
+      <c r="F52" s="32" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="G52" s="32" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="H52" s="30" t="n">
+        <v>4</v>
       </c>
       <c r="I52" s="33" t="s">
         <v>119</v>
       </c>
       <c r="J52" s="34" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="K52" s="35" t="s">
         <v>121</v>
       </c>
       <c r="L52" s="34" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="36" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B53" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C53" s="38" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="40" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B53" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="D53" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="E53" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="F53" s="39" t="n">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="G53" s="39" t="n">
-        <v>0.420833333333333</v>
-      </c>
-      <c r="H53" s="37" t="n">
-        <v>3</v>
+      <c r="D53" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="E53" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="F53" s="43" t="n">
+        <v>0.397222222222222</v>
+      </c>
+      <c r="G53" s="43" t="n">
+        <v>0.472222222222222</v>
+      </c>
+      <c r="H53" s="41" t="n">
+        <v>2</v>
       </c>
       <c r="I53" s="33" t="s">
         <v>122</v>
       </c>
       <c r="J53" s="34" t="n">
+        <v>65</v>
+      </c>
+      <c r="K53" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="L53" s="34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="36" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B54" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="D54" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="F54" s="39" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="G54" s="39" t="n">
+        <v>0.420833333333333</v>
+      </c>
+      <c r="H54" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I54" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="J54" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="K53" s="35" t="s">
+      <c r="K54" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="L53" s="34" t="s">
+      <c r="L54" s="34" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="29" t="n">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="29" t="n">
         <v>46319</v>
       </c>
-      <c r="B54" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="D54" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E54" s="30" t="s">
+      <c r="B55" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D55" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="F54" s="32" t="n">
+      <c r="F55" s="32" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="G54" s="32" t="n">
+      <c r="G55" s="32" t="n">
         <v>0.395833333333333</v>
       </c>
-      <c r="H54" s="30" t="n">
+      <c r="H55" s="30" t="n">
         <v>2</v>
-      </c>
-      <c r="I54" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="J54" s="34"/>
-      <c r="K54" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="L54" s="34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="40" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B55" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="C55" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="D55" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="E55" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="F55" s="43" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="G55" s="43" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="H55" s="41" t="n">
-        <v>4</v>
       </c>
       <c r="I55" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="J55" s="34" t="n">
-        <v>30</v>
-      </c>
+      <c r="J55" s="34"/>
       <c r="K55" s="35" t="s">
         <v>129</v>
       </c>
@@ -7508,9 +7566,47 @@
         <v>62</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="20" t="s">
-        <v>159</v>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="29" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B56" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F56" s="32" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="G56" s="32" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H56" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="J56" s="34" t="n">
+        <v>22</v>
+      </c>
+      <c r="K56" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="L56" s="34" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="20" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -7541,7 +7637,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7549,16 +7645,16 @@
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7569,7 +7665,7 @@
         <v>5.9</v>
       </c>
       <c r="C4" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$R$3:$R$56,A4)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A4)</f>
         <v>5.9</v>
       </c>
       <c r="D4" s="46" t="n">
@@ -7589,7 +7685,7 @@
         <v>776</v>
       </c>
       <c r="C5" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$R$3:$R$56,A5)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A5)</f>
         <v>776</v>
       </c>
       <c r="D5" s="46" t="n">
@@ -7609,7 +7705,7 @@
         <v>22.5</v>
       </c>
       <c r="C6" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$R$3:$R$56,A6)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A6)</f>
         <v>22.5</v>
       </c>
       <c r="D6" s="46" t="n">
@@ -7629,7 +7725,7 @@
         <v>101</v>
       </c>
       <c r="C7" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$R$3:$R$56,A7)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A7)</f>
         <v>101</v>
       </c>
       <c r="D7" s="46" t="n">
@@ -7646,11 +7742,11 @@
         <v>62</v>
       </c>
       <c r="B8" s="45" t="n">
-        <v>58.3333</v>
+        <v>72.3333</v>
       </c>
       <c r="C8" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$R$3:$R$56,A8)</f>
-        <v>58.3333333333333</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A8)</f>
+        <v>72.3333333333333</v>
       </c>
       <c r="D8" s="46" t="n">
         <f aca="false">C8-B8</f>
@@ -7669,7 +7765,7 @@
         <v>5.8333</v>
       </c>
       <c r="C9" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$R$3:$R$56,A9)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A9)</f>
         <v>5.6</v>
       </c>
       <c r="D9" s="46" t="n">
@@ -7689,7 +7785,7 @@
         <v>816</v>
       </c>
       <c r="C10" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$R$3:$R$56,A10)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A10)</f>
         <v>816</v>
       </c>
       <c r="D10" s="46" t="n">
@@ -7709,7 +7805,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$R$3:$R$56,A11)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A11)</f>
         <v>9</v>
       </c>
       <c r="D11" s="46" t="n">
@@ -7729,7 +7825,7 @@
         <v>32</v>
       </c>
       <c r="C12" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$56,'S32 5-10 đến 24-10'!$R$3:$R$56,A12)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A12)</f>
         <v>32</v>
       </c>
       <c r="D12" s="46" t="n">
@@ -7743,15 +7839,15 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="47" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B13" s="48" t="n">
         <f aca="false">SUM(B4:B12)</f>
-        <v>1826.5666</v>
+        <v>1840.5666</v>
       </c>
       <c r="C13" s="48" t="n">
         <f aca="false">SUM(C4:C12)</f>
-        <v>1826.33333333333</v>
+        <v>1840.33333333333</v>
       </c>
       <c r="D13" s="48" t="n">
         <f aca="false">SUM(D4:D12)</f>
@@ -7764,7 +7860,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -7795,19 +7891,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7818,10 +7914,10 @@
         <v>26</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E2" s="26" t="n">
         <v>10</v>
@@ -7835,10 +7931,10 @@
         <v>26</v>
       </c>
       <c r="C3" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" s="26" t="s">
         <v>171</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>170</v>
       </c>
       <c r="E3" s="26" t="n">
         <v>5</v>
@@ -7852,10 +7948,10 @@
         <v>26</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>10</v>
@@ -7869,10 +7965,10 @@
         <v>26</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E5" s="26" t="n">
         <v>27</v>
@@ -7886,10 +7982,10 @@
         <v>26</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>23</v>
@@ -7903,10 +7999,10 @@
         <v>26</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>27</v>
@@ -7920,10 +8016,10 @@
         <v>26</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>23</v>
@@ -7937,10 +8033,10 @@
         <v>62</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E9" s="26" t="n">
         <v>50</v>
@@ -7954,10 +8050,10 @@
         <v>62</v>
       </c>
       <c r="C10" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="26" t="s">
         <v>179</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>178</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>100</v>
@@ -7971,10 +8067,10 @@
         <v>65</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E11" s="26" t="n">
         <v>13</v>
@@ -7988,10 +8084,10 @@
         <v>65</v>
       </c>
       <c r="C12" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12" s="26" t="s">
         <v>182</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>181</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>13</v>
@@ -8005,10 +8101,10 @@
         <v>65</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E13" s="26" t="n">
         <v>13</v>
@@ -8022,10 +8118,10 @@
         <v>65</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>13</v>
@@ -8039,10 +8135,10 @@
         <v>65</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E15" s="26" t="n">
         <v>13</v>
@@ -8056,10 +8152,10 @@
         <v>65</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>13</v>
@@ -8073,10 +8169,10 @@
         <v>65</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E17" s="26" t="n">
         <v>13</v>
@@ -8090,10 +8186,10 @@
         <v>65</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E18" s="26" t="n">
         <v>13</v>
@@ -8107,10 +8203,10 @@
         <v>65</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E19" s="26" t="n">
         <v>13</v>
@@ -8124,10 +8220,10 @@
         <v>65</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E20" s="26" t="n">
         <v>13</v>
@@ -8141,10 +8237,10 @@
         <v>65</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E21" s="26" t="n">
         <v>13</v>
@@ -8158,10 +8254,10 @@
         <v>65</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E22" s="26" t="n">
         <v>13</v>
@@ -8175,10 +8271,10 @@
         <v>65</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E23" s="26" t="n">
         <v>13</v>
@@ -8192,10 +8288,10 @@
         <v>65</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E24" s="26" t="n">
         <v>13</v>
@@ -8209,10 +8305,10 @@
         <v>65</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E25" s="26" t="n">
         <v>455</v>
@@ -8226,10 +8322,10 @@
         <v>65</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>299</v>
@@ -8243,10 +8339,10 @@
         <v>65</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>286</v>
@@ -8260,10 +8356,10 @@
         <v>65</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E28" s="26" t="n">
         <v>1092</v>
@@ -8277,10 +8373,10 @@
         <v>65</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E29" s="26" t="n">
         <v>156</v>
@@ -8294,10 +8390,10 @@
         <v>65</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E30" s="26" t="n">
         <v>13</v>
@@ -8311,10 +8407,10 @@
         <v>65</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E31" s="26" t="n">
         <v>13</v>
@@ -8328,10 +8424,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E32" s="26" t="n">
         <v>13</v>
@@ -8345,10 +8441,10 @@
         <v>65</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E33" s="26" t="n">
         <v>13</v>
@@ -8365,7 +8461,7 @@
         <v>74</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E34" s="26" t="n">
         <v>100</v>
@@ -8382,7 +8478,7 @@
         <v>80</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E35" s="26" t="n">
         <v>4</v>
@@ -8399,7 +8495,7 @@
         <v>109</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E36" s="26" t="n">
         <v>30</v>
@@ -8416,7 +8512,7 @@
         <v>110</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E37" s="26" t="n">
         <v>2</v>
@@ -8433,7 +8529,7 @@
         <v>114</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E38" s="26" t="n">
         <v>30</v>
@@ -8447,10 +8543,10 @@
         <v>79</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E39" s="26" t="n">
         <v>65</v>
@@ -8464,13 +8560,13 @@
         <v>62</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -8497,77 +8593,77 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="51" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="51" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="51" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="51" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="51" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="51" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="51" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="51" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="51" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="51" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="51" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="51" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="51" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="51" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/loss-time/outputs/Loss_time_S32_05-10_den_24-10.xlsx
+++ b/loss-time/outputs/Loss_time_S32_05-10_den_24-10.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Ghi chú review" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'S32 5-10 đến 24-10'!$A$2:$R$57</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'S32 5-10 đến 24-10'!$A$2:$R$80</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="226">
   <si>
     <t xml:space="preserve">LOSS TIME MÃ S32 (OTHER SUPPORT OF PRODUCTION) - 05/10 ĐẾN 24/10/2026 - LÀM RIÊNG, KHÔNG LẪN MÃ KHÁC</t>
   </si>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">1. Bảng này CHỈ chứa mã S32, tách hoàn toàn khỏi bảng P20/P26/P22/A2 (không lẫn mã khác). Khi bạn cập nhật, tôi giữ nguyên nguyên tắc này.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Nguồn: 5 file trong gói zip (lấy bản mới nhất mỗi loại: Beam saw bản 24/10, UV bản (1), Ép nóng bản (1), Veneer bản mới nhất 24/10, file sửa hàng MAC Mr.Hiệp) và 3 hình (thợ sơn tuần 42, cào cước 16/10, bắn cát 15/10). Chỉ lấy dòng từ 05/10 đến 24/10. UV (báo cáo ngày đến 11/10, phát sinh đến 13/10) và Ép nóng (đến 6/10) chưa có số liệu mới.</t>
+    <t xml:space="preserve">2. Nguồn: 5 file trong gói zip (lấy bản mới nhất mỗi loại: Beam saw bản 24/10, UV bản 24/10, Ép nóng bản (1), Veneer bản mới nhất 24/10, file sửa hàng MAC Mr.Hiệp) và 3 hình (thợ sơn tuần 42, cào cước 16/10, bắn cát 15/10). Chỉ lấy dòng từ 05/10 đến 24/10. Ép nóng (đến 6/10) chưa có số liệu mới. UV báo cáo ngày nay có đến 24/10; phát sinh đến 13/10.</t>
   </si>
   <si>
     <t xml:space="preserve">3. Tất cả giờ công trong bảng khớp với số giờ trong nguồn (sheet "Đối chiếu nguồn"). Tổng giờ công xem sheet "Đối chiếu nguồn".</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">5. UV Chủ nhật 11/10: có 9 người làm 8 giờ (72 giờ). Cần xác nhận có nhập Chủ nhật không (tô cam).</t>
   </si>
   <si>
-    <t xml:space="preserve">6. UV: file báo cáo ngày chỉ đến 11/10; chưa có số liệu từ 12/10. UV phát sinh 12/10 có 23 mã hàng SLAT nhưng chỉ 2 dòng có giờ (HC 1, 9:30-20:00 và 7:30-15:00); danh sách mã ở sheet "Chi tiết mã hàng". Bộ phận ghi "QC" (báo cáo ghi "QC A HIẾU"), cần xác nhận.</t>
+    <t xml:space="preserve">6. UV báo cáo ngày (file mới 24/10): từ 12/10 đến 24/10 là các dòng mới; 5/10-11/10 không đổi. File có nhiều khối W42 bị lặp (12/10-18/10 xuất hiện 2 lần, giống hệt nhau), bảng chỉ tính một lần. Chủ nhật 18/10 và 25/10 không có HC làm việc nên không ghi. UV phát sinh 12/10 có 23 mã hàng SLAT nhưng chỉ 2 dòng có giờ (HC 1, 9:30-20:00 và 7:30-15:00); danh sách mã ở sheet "Chi tiết mã hàng". Bộ phận ghi "QC" (báo cáo ghi "QC A HIẾU"), cần xác nhận. Sheet UV phát sinh chỉ đổi nhãn tuần W41 thành W42.</t>
   </si>
   <si>
     <t xml:space="preserve">7. Beam saw: 17 dòng có giờ từ 08/10 đến 24/10 (thêm 22/10: AR1337F1291 0,1 giờ FINISHING và W4012F2041 3 giờ hàng bảng màu; 24/10: AT655F535 0,3 giờ). Dòng CZ567F09 ngày 20/10 đã được sửa trong file nguồn thành 18:15-18:18. 3 dòng ngày 19/10 (18:00-18:07) trên hệ thống đang nhập ngày 18/10, nguồn ghi ngày 19/10, cần kiểm tra lại. Khu vực ghi RC - PANEL (Raw Cutting, người dùng xác nhận 20/10). Bộ phận lấy từ cột Charge to: Machining CNC và Machining ghi "Machining"; "QA ..." ghi "QC"; 5 dòng ngày 16/10, 20/10 và 24/10 là "Unassigned" (chưa phân công), cần xác định bộ phận (tô cam).</t>
@@ -1398,7 +1398,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R83"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -2694,7 +2694,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B26,21)</f>
         <v>W42</v>
@@ -2716,36 +2716,36 @@
         <v>22</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>0.3125</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.625</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="O26" s="7" t="n">
         <f aca="false">(N26-M26)*24</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q26" s="7" t="n">
         <f aca="false">P26*O26</f>
-        <v>7.5</v>
+        <v>88</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B27,21)</f>
         <v>W42</v>
@@ -2753,13 +2753,9 @@
       <c r="B27" s="4" t="n">
         <v>46307</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>66</v>
-      </c>
+      <c r="C27" s="5"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="3" t="n">
-        <v>2522</v>
-      </c>
+      <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
         <v>20</v>
@@ -2771,36 +2767,36 @@
         <v>22</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.395833333333333</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.833333333333333</v>
+        <v>0.8125</v>
       </c>
       <c r="O27" s="7" t="n">
         <f aca="false">(N27-M27)*24</f>
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q27" s="7" t="n">
         <f aca="false">P27*O27</f>
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B28,21)</f>
         <v>W42</v>
@@ -2813,7 +2809,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>21</v>
@@ -2822,49 +2818,49 @@
         <v>22</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="M28" s="6" t="n">
         <v>0.3125</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
       <c r="O28" s="7" t="n">
         <f aca="false">(N28-M28)*24</f>
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="7" t="n">
         <f aca="false">P28*O28</f>
-        <v>144</v>
+        <v>7.5</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B29,21)</f>
         <v>W42</v>
       </c>
       <c r="B29" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3" t="n">
-        <v>9</v>
+        <v>2522</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
@@ -2877,30 +2873,30 @@
         <v>22</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.645833333333333</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="N29" s="6" t="n">
         <v>0.833333333333333</v>
       </c>
       <c r="O29" s="7" t="n">
         <f aca="false">(N29-M29)*24</f>
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q29" s="7" t="n">
         <f aca="false">P29*O29</f>
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>65</v>
@@ -2912,7 +2908,7 @@
         <v>W42</v>
       </c>
       <c r="B30" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="3"/>
@@ -2957,24 +2953,20 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B31,21)</f>
         <v>W42</v>
       </c>
       <c r="B31" s="4" t="n">
-        <v>46309</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>74</v>
-      </c>
+        <v>46308</v>
+      </c>
+      <c r="C31" s="5"/>
       <c r="D31" s="3"/>
-      <c r="E31" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>21</v>
@@ -2983,33 +2975,33 @@
         <v>22</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.375</v>
+        <v>0.3125</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.416666666666667</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="O31" s="7" t="n">
         <f aca="false">(N31-M31)*24</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q31" s="7" t="n">
         <f aca="false">P31*O31</f>
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3018,14 +3010,14 @@
         <v>W42</v>
       </c>
       <c r="B32" s="4" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>21</v>
@@ -3037,30 +3029,30 @@
         <v>30</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.3125</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>0.8125</v>
       </c>
       <c r="O32" s="7" t="n">
         <f aca="false">(N32-M32)*24</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q32" s="7" t="n">
         <f aca="false">P32*O32</f>
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3069,14 +3061,14 @@
         <v>W42</v>
       </c>
       <c r="B33" s="4" t="n">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
@@ -3089,33 +3081,33 @@
         <v>22</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.333333333333333</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.347222222222222</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O33" s="7" t="n">
         <f aca="false">(N33-M33)*24</f>
-        <v>0.333333333333333</v>
+        <v>4.5</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q33" s="7" t="n">
         <f aca="false">P33*O33</f>
-        <v>0.333333333333333</v>
+        <v>4.5</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3124,7 +3116,7 @@
         <v>W42</v>
       </c>
       <c r="B34" s="4" t="n">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="3"/>
@@ -3170,168 +3162,160 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="str">
+      <c r="A35" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B35,21)</f>
         <v>W42</v>
       </c>
-      <c r="B35" s="14" t="n">
-        <v>46310</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13" t="n">
-        <v>734</v>
-      </c>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I35" s="15" t="s">
+      <c r="B35" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I35" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J35" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="L35" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="M35" s="16" t="n">
-        <v>0.291666666666667</v>
-      </c>
-      <c r="N35" s="16" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O35" s="17" t="n">
+      <c r="J35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="O35" s="7" t="n">
         <f aca="false">(N35-M35)*24</f>
         <v>8</v>
       </c>
-      <c r="P35" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q35" s="17" t="n">
+      <c r="P35" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q35" s="7" t="n">
         <f aca="false">P35*O35</f>
-        <v>32</v>
-      </c>
-      <c r="R35" s="13" t="s">
-        <v>85</v>
+        <v>96</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="str">
+      <c r="A36" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B36,21)</f>
         <v>W42</v>
       </c>
-      <c r="B36" s="9" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="10" t="s">
+      <c r="B36" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J36" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K36" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="L36" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="M36" s="11" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="N36" s="11" t="n">
-        <v>0.336805555555556</v>
-      </c>
-      <c r="O36" s="12" t="n">
+      <c r="J36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="N36" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="O36" s="7" t="n">
         <f aca="false">(N36-M36)*24</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="P36" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q36" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q36" s="7" t="n">
         <f aca="false">P36*O36</f>
-        <v>0.25</v>
-      </c>
-      <c r="R36" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="str">
+        <v>36</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B37,21)</f>
         <v>W42</v>
       </c>
-      <c r="B37" s="9" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37" s="10" t="s">
+      <c r="B37" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J37" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K37" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="L37" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="M37" s="11" t="n">
-        <v>0.336805555555556</v>
-      </c>
-      <c r="N37" s="11" t="n">
-        <v>0.34375</v>
-      </c>
-      <c r="O37" s="12" t="n">
+      <c r="J37" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="M37" s="6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="N37" s="6" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="O37" s="7" t="n">
         <f aca="false">(N37-M37)*24</f>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="P37" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" s="7" t="n">
         <f aca="false">P37*O37</f>
-        <v>0.5</v>
-      </c>
-      <c r="R37" s="8" t="s">
-        <v>41</v>
+        <v>2</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3340,7 +3324,7 @@
         <v>W42</v>
       </c>
       <c r="B38" s="4" t="n">
-        <v>46311</v>
+        <v>46309</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="3"/>
@@ -3391,16 +3375,14 @@
         <v>W42</v>
       </c>
       <c r="B39" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>91</v>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="C39" s="5"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>21</v>
@@ -3409,86 +3391,84 @@
         <v>22</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="L39" s="5" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.333333333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.5</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="O39" s="7" t="n">
         <f aca="false">(N39-M39)*24</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q39" s="7" t="n">
         <f aca="false">P39*O39</f>
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="str">
+      <c r="A40" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B40,21)</f>
         <v>W42</v>
       </c>
-      <c r="B40" s="14" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H40" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40" s="15" t="s">
+      <c r="B40" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J40" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K40" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="L40" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="M40" s="16" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N40" s="16" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="O40" s="17" t="n">
+      <c r="J40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="N40" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="O40" s="7" t="n">
         <f aca="false">(N40-M40)*24</f>
-        <v>5</v>
-      </c>
-      <c r="P40" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q40" s="7" t="n">
         <f aca="false">P40*O40</f>
-        <v>5</v>
-      </c>
-      <c r="R40" s="13" t="s">
-        <v>94</v>
+        <v>36</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3497,10 +3477,10 @@
         <v>W42</v>
       </c>
       <c r="B41" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="n">
@@ -3517,156 +3497,152 @@
         <v>22</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.541666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.544444444444444</v>
+        <v>0.347222222222222</v>
       </c>
       <c r="O41" s="7" t="n">
         <f aca="false">(N41-M41)*24</f>
-        <v>0.0666666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="7" t="n">
         <f aca="false">P41*O41</f>
-        <v>0.2</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13" t="str">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B42,21)</f>
         <v>W42</v>
       </c>
-      <c r="B42" s="14" t="n">
-        <v>46312</v>
-      </c>
-      <c r="C42" s="15"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13" t="s">
+      <c r="B42" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H42" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I42" s="15" t="s">
+      <c r="H42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J42" s="13" t="s">
+      <c r="J42" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K42" s="15" t="s">
+      <c r="K42" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="L42" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="M42" s="16" t="n">
+      <c r="L42" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="M42" s="6" t="n">
         <v>0.3125</v>
       </c>
-      <c r="N42" s="16" t="n">
-        <v>0.645833333333333</v>
-      </c>
-      <c r="O42" s="17" t="n">
+      <c r="N42" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="O42" s="7" t="n">
         <f aca="false">(N42-M42)*24</f>
+        <v>12</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q42" s="7" t="n">
+        <f aca="false">P42*O42</f>
+        <v>144</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B43,21)</f>
+        <v>W42</v>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13" t="n">
+        <v>734</v>
+      </c>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="M43" s="16" t="n">
+        <v>0.291666666666667</v>
+      </c>
+      <c r="N43" s="16" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O43" s="17" t="n">
+        <f aca="false">(N43-M43)*24</f>
         <v>8</v>
       </c>
-      <c r="P42" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q42" s="17" t="n">
-        <f aca="false">P42*O42</f>
-        <v>96</v>
-      </c>
-      <c r="R42" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="str">
-        <f aca="false">"W"&amp;WEEKNUM(B43,21)</f>
-        <v>W43</v>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>46314</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="L43" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="M43" s="6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N43" s="6" t="n">
-        <v>0.751388888888889</v>
-      </c>
-      <c r="O43" s="7" t="n">
-        <f aca="false">(N43-M43)*24</f>
-        <v>0.0333333333333333</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="7" t="n">
+      <c r="P43" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="17" t="n">
         <f aca="false">P43*O43</f>
-        <v>0.1</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>41</v>
+        <v>32</v>
+      </c>
+      <c r="R43" s="13" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B44,21)</f>
-        <v>W43</v>
+        <v>W42</v>
       </c>
       <c r="B44" s="4" t="n">
-        <v>46314</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>100</v>
-      </c>
+        <v>46311</v>
+      </c>
+      <c r="C44" s="5"/>
       <c r="D44" s="3"/>
-      <c r="E44" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>20</v>
@@ -3678,50 +3654,46 @@
         <v>22</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.751388888888889</v>
+        <v>0.3125</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.752777777777778</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="O44" s="7" t="n">
         <f aca="false">(N44-M44)*24</f>
-        <v>0.0333333333333333</v>
+        <v>8</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q44" s="7" t="n">
         <f aca="false">P44*O44</f>
-        <v>0.1</v>
+        <v>80</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B45,21)</f>
-        <v>W43</v>
+        <v>W42</v>
       </c>
       <c r="B45" s="4" t="n">
-        <v>46314</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>97</v>
-      </c>
+        <v>46311</v>
+      </c>
+      <c r="C45" s="5"/>
       <c r="D45" s="3"/>
-      <c r="E45" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>20</v>
@@ -3733,49 +3705,49 @@
         <v>22</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.752777777777778</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.754861111111111</v>
+        <v>0.8125</v>
       </c>
       <c r="O45" s="7" t="n">
         <f aca="false">(N45-M45)*24</f>
-        <v>0.05</v>
+        <v>4</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q45" s="7" t="n">
         <f aca="false">P45*O45</f>
-        <v>0.15</v>
+        <v>36</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B46,21)</f>
-        <v>W43</v>
+        <v>W42</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>46315</v>
+        <v>46311</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8" t="s">
@@ -3791,16 +3763,16 @@
         <v>87</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="L46" s="10" t="s">
         <v>89</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.756944444444444</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="N46" s="11" t="n">
-        <v>0.760416666666667</v>
+        <v>0.336805555555556</v>
       </c>
       <c r="O46" s="12" t="n">
         <f aca="false">(N46-M46)*24</f>
@@ -3820,17 +3792,17 @@
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B47,21)</f>
-        <v>W43</v>
+        <v>W42</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>46315</v>
+        <v>46311</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8" t="s">
@@ -3846,27 +3818,27 @@
         <v>87</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="L47" s="10" t="s">
         <v>89</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.760416666666667</v>
+        <v>0.336805555555556</v>
       </c>
       <c r="N47" s="11" t="n">
-        <v>0.7625</v>
+        <v>0.34375</v>
       </c>
       <c r="O47" s="12" t="n">
         <f aca="false">(N47-M47)*24</f>
-        <v>0.05</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="P47" s="8" t="n">
         <v>3</v>
       </c>
       <c r="Q47" s="12" t="n">
         <f aca="false">P47*O47</f>
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="R47" s="8" t="s">
         <v>41</v>
@@ -3875,21 +3847,17 @@
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B48,21)</f>
-        <v>W43</v>
+        <v>W42</v>
       </c>
       <c r="B48" s="4" t="n">
-        <v>46315</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>109</v>
-      </c>
+        <v>46311</v>
+      </c>
+      <c r="C48" s="5"/>
       <c r="D48" s="3"/>
-      <c r="E48" s="3" t="n">
-        <v>30</v>
-      </c>
+      <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>21</v>
@@ -3898,160 +3866,152 @@
         <v>22</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="L48" s="5" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.375</v>
+        <v>0.3125</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>0.409722222222222</v>
+        <v>0.8125</v>
       </c>
       <c r="O48" s="7" t="n">
         <f aca="false">(N48-M48)*24</f>
-        <v>0.833333333333333</v>
+        <v>12</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q48" s="7" t="n">
         <f aca="false">P48*O48</f>
+        <v>144</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B49,21)</f>
+        <v>W42</v>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="L49" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O49" s="7" t="n">
+        <f aca="false">(N49-M49)*24</f>
+        <v>4</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="7" t="n">
+        <f aca="false">P49*O49</f>
+        <v>4</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="13" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B50,21)</f>
+        <v>W42</v>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J50" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K50" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="L50" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="M50" s="16" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N50" s="16" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="str">
-        <f aca="false">"W"&amp;WEEKNUM(B49,21)</f>
-        <v>W43</v>
-      </c>
-      <c r="B49" s="9" t="n">
-        <v>46315</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J49" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="K49" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="M49" s="11" t="n">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="N49" s="11" t="n">
-        <v>0.46875</v>
-      </c>
-      <c r="O49" s="12" t="n">
-        <f aca="false">(N49-M49)*24</f>
-        <v>1.25</v>
-      </c>
-      <c r="P49" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q49" s="12" t="n">
-        <f aca="false">P49*O49</f>
-        <v>2.5</v>
-      </c>
-      <c r="R49" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="str">
-        <f aca="false">"W"&amp;WEEKNUM(B50,21)</f>
-        <v>W43</v>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>46315</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="K50" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="L50" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="M50" s="6" t="n">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="N50" s="6" t="n">
-        <v>0.444444444444444</v>
-      </c>
-      <c r="O50" s="7" t="n">
+      <c r="O50" s="17" t="n">
         <f aca="false">(N50-M50)*24</f>
-        <v>0.666666666666667</v>
-      </c>
-      <c r="P50" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P50" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" s="7" t="n">
+      <c r="Q50" s="17" t="n">
         <f aca="false">P50*O50</f>
-        <v>0.666666666666667</v>
-      </c>
-      <c r="R50" s="3" t="s">
-        <v>62</v>
+        <v>5</v>
+      </c>
+      <c r="R50" s="13" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B51,21)</f>
-        <v>W43</v>
+        <v>W42</v>
       </c>
       <c r="B51" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>115</v>
-      </c>
+        <v>46312</v>
+      </c>
+      <c r="C51" s="5"/>
       <c r="D51" s="3"/>
-      <c r="E51" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>20</v>
@@ -4066,47 +4026,43 @@
         <v>30</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="L51" s="5" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.333333333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.334722222222222</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="O51" s="7" t="n">
         <f aca="false">(N51-M51)*24</f>
-        <v>0.0333333333333333</v>
+        <v>8</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q51" s="7" t="n">
         <f aca="false">P51*O51</f>
-        <v>0.1</v>
+        <v>96</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B52,21)</f>
-        <v>W43</v>
+        <v>W42</v>
       </c>
       <c r="B52" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>117</v>
-      </c>
+        <v>46312</v>
+      </c>
+      <c r="C52" s="5"/>
       <c r="D52" s="3"/>
-      <c r="E52" s="3" t="n">
-        <v>20</v>
-      </c>
+      <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>20</v>
@@ -4118,49 +4074,49 @@
         <v>22</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="L52" s="5" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.375</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.416666666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="O52" s="7" t="n">
         <f aca="false">(N52-M52)*24</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P52" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q52" s="7" t="n">
         <f aca="false">P52*O52</f>
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B53,21)</f>
-        <v>W43</v>
+        <v>W42</v>
       </c>
       <c r="B53" s="4" t="n">
-        <v>46318</v>
+        <v>46312</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
@@ -4173,53 +4129,49 @@
         <v>22</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="L53" s="5" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.333333333333333</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.833333333333333</v>
+        <v>0.544444444444444</v>
       </c>
       <c r="O53" s="7" t="n">
         <f aca="false">(N53-M53)*24</f>
-        <v>12</v>
+        <v>0.0666666666666667</v>
       </c>
       <c r="P53" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q53" s="7" t="n">
         <f aca="false">P53*O53</f>
-        <v>48</v>
+        <v>0.2</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B54,21)</f>
-        <v>W43</v>
+        <v>W42</v>
       </c>
       <c r="B54" s="14" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>122</v>
-      </c>
+        <v>46312</v>
+      </c>
+      <c r="C54" s="15"/>
       <c r="D54" s="13"/>
-      <c r="E54" s="13" t="n">
-        <v>65</v>
-      </c>
+      <c r="E54" s="13"/>
       <c r="F54" s="13"/>
       <c r="G54" s="13" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H54" s="13" t="s">
         <v>21</v>
@@ -4228,88 +4180,84 @@
         <v>22</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="L54" s="15" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="M54" s="16" t="n">
-        <v>0.397222222222222</v>
+        <v>0.3125</v>
       </c>
       <c r="N54" s="16" t="n">
-        <v>0.472222222222222</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="O54" s="17" t="n">
         <f aca="false">(N54-M54)*24</f>
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="P54" s="13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q54" s="17" t="n">
         <f aca="false">P54*O54</f>
-        <v>3.6</v>
+        <v>96</v>
       </c>
       <c r="R54" s="13" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="8" t="str">
+      <c r="A55" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B55,21)</f>
         <v>W43</v>
       </c>
-      <c r="B55" s="9" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H55" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55" s="10" t="s">
+      <c r="B55" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C55" s="5"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I55" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J55" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K55" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="L55" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="M55" s="11" t="n">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="N55" s="11" t="n">
-        <v>0.420833333333333</v>
-      </c>
-      <c r="O55" s="12" t="n">
+      <c r="J55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L55" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M55" s="6" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="O55" s="7" t="n">
         <f aca="false">(N55-M55)*24</f>
-        <v>0.1</v>
-      </c>
-      <c r="P55" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q55" s="7" t="n">
         <f aca="false">P55*O55</f>
-        <v>0.3</v>
-      </c>
-      <c r="R55" s="8" t="s">
-        <v>41</v>
+        <v>96</v>
+      </c>
+      <c r="R55" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4318,11 +4266,9 @@
         <v>W43</v>
       </c>
       <c r="B56" s="4" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>127</v>
-      </c>
+        <v>46314</v>
+      </c>
+      <c r="C56" s="5"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -4336,33 +4282,33 @@
         <v>22</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="L56" s="5" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.333333333333333</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.395833333333333</v>
+        <v>0.8125</v>
       </c>
       <c r="O56" s="7" t="n">
         <f aca="false">(N56-M56)*24</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q56" s="7" t="n">
         <f aca="false">P56*O56</f>
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4371,14 +4317,14 @@
         <v>W43</v>
       </c>
       <c r="B57" s="4" t="n">
-        <v>46319</v>
+        <v>46314</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
@@ -4391,51 +4337,1278 @@
         <v>22</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="L57" s="5" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.625</v>
+        <v>0.751388888888889</v>
       </c>
       <c r="O57" s="7" t="n">
         <f aca="false">(N57-M57)*24</f>
-        <v>7</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q57" s="7" t="n">
         <f aca="false">P57*O57</f>
+        <v>0.1</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B58,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="L58" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>0.751388888888889</v>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>0.752777777777778</v>
+      </c>
+      <c r="O58" s="7" t="n">
+        <f aca="false">(N58-M58)*24</f>
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="P58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="7" t="n">
+        <f aca="false">P58*O58</f>
+        <v>0.1</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B59,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L59" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M59" s="6" t="n">
+        <v>0.752777777777778</v>
+      </c>
+      <c r="N59" s="6" t="n">
+        <v>0.754861111111111</v>
+      </c>
+      <c r="O59" s="7" t="n">
+        <f aca="false">(N59-M59)*24</f>
+        <v>0.05</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="7" t="n">
+        <f aca="false">P59*O59</f>
+        <v>0.15</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B60,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C60" s="5"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L60" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N60" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="O60" s="7" t="n">
+        <f aca="false">(N60-M60)*24</f>
+        <v>8</v>
+      </c>
+      <c r="P60" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q60" s="7" t="n">
+        <f aca="false">P60*O60</f>
+        <v>96</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B61,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C61" s="5"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M61" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="N61" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="O61" s="7" t="n">
+        <f aca="false">(N61-M61)*24</f>
+        <v>4</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q61" s="7" t="n">
+        <f aca="false">P61*O61</f>
+        <v>40</v>
+      </c>
+      <c r="R61" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="8" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B62,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B62" s="9" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K62" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="L62" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="M62" s="11" t="n">
+        <v>0.756944444444444</v>
+      </c>
+      <c r="N62" s="11" t="n">
+        <v>0.760416666666667</v>
+      </c>
+      <c r="O62" s="12" t="n">
+        <f aca="false">(N62-M62)*24</f>
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="P62" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="12" t="n">
+        <f aca="false">P62*O62</f>
+        <v>0.25</v>
+      </c>
+      <c r="R62" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="8" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B63,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" s="8"/>
+      <c r="G63" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="M63" s="11" t="n">
+        <v>0.760416666666667</v>
+      </c>
+      <c r="N63" s="11" t="n">
+        <v>0.7625</v>
+      </c>
+      <c r="O63" s="12" t="n">
+        <f aca="false">(N63-M63)*24</f>
+        <v>0.05</v>
+      </c>
+      <c r="P63" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q63" s="12" t="n">
+        <f aca="false">P63*O63</f>
+        <v>0.15</v>
+      </c>
+      <c r="R63" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B64,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B64" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K64" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L64" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="M64" s="6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="N64" s="6" t="n">
+        <v>0.409722222222222</v>
+      </c>
+      <c r="O64" s="7" t="n">
+        <f aca="false">(N64-M64)*24</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="7" t="n">
+        <f aca="false">P64*O64</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="R64" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="8" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B65,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K65" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="L65" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="M65" s="11" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="N65" s="11" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="O65" s="12" t="n">
+        <f aca="false">(N65-M65)*24</f>
+        <v>1.25</v>
+      </c>
+      <c r="P65" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q65" s="12" t="n">
+        <f aca="false">P65*O65</f>
+        <v>2.5</v>
+      </c>
+      <c r="R65" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B66,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L66" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="M66" s="6" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="N66" s="6" t="n">
+        <v>0.444444444444444</v>
+      </c>
+      <c r="O66" s="7" t="n">
+        <f aca="false">(N66-M66)*24</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="7" t="n">
+        <f aca="false">P66*O66</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B67,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B67" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="C67" s="5"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L67" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M67" s="6" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N67" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="O67" s="7" t="n">
+        <f aca="false">(N67-M67)*24</f>
+        <v>8</v>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q67" s="7" t="n">
+        <f aca="false">P67*O67</f>
+        <v>96</v>
+      </c>
+      <c r="R67" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B68,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B68" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="C68" s="5"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L68" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M68" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="N68" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="O68" s="7" t="n">
+        <f aca="false">(N68-M68)*24</f>
+        <v>4</v>
+      </c>
+      <c r="P68" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q68" s="7" t="n">
+        <f aca="false">P68*O68</f>
+        <v>32</v>
+      </c>
+      <c r="R68" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B69,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B69" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C69" s="5"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L69" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M69" s="6" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N69" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="O69" s="7" t="n">
+        <f aca="false">(N69-M69)*24</f>
+        <v>8</v>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q69" s="7" t="n">
+        <f aca="false">P69*O69</f>
+        <v>80</v>
+      </c>
+      <c r="R69" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B70,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B70" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C70" s="5"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L70" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M70" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="N70" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="O70" s="7" t="n">
+        <f aca="false">(N70-M70)*24</f>
+        <v>4</v>
+      </c>
+      <c r="P70" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q70" s="7" t="n">
+        <f aca="false">P70*O70</f>
+        <v>28</v>
+      </c>
+      <c r="R70" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B71,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B71" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K71" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L71" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="M71" s="6" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N71" s="6" t="n">
+        <v>0.334722222222222</v>
+      </c>
+      <c r="O71" s="7" t="n">
+        <f aca="false">(N71-M71)*24</f>
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q71" s="7" t="n">
+        <f aca="false">P71*O71</f>
+        <v>0.1</v>
+      </c>
+      <c r="R71" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B72,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K72" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L72" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="M72" s="6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="N72" s="6" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="O72" s="7" t="n">
+        <f aca="false">(N72-M72)*24</f>
+        <v>1</v>
+      </c>
+      <c r="P72" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="7" t="n">
+        <f aca="false">P72*O72</f>
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B73,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B73" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C73" s="5"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L73" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M73" s="6" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N73" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="O73" s="7" t="n">
+        <f aca="false">(N73-M73)*24</f>
+        <v>8</v>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q73" s="7" t="n">
+        <f aca="false">P73*O73</f>
+        <v>96</v>
+      </c>
+      <c r="R73" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B74,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C74" s="5"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L74" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M74" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="N74" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="O74" s="7" t="n">
+        <f aca="false">(N74-M74)*24</f>
+        <v>4</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q74" s="7" t="n">
+        <f aca="false">P74*O74</f>
+        <v>32</v>
+      </c>
+      <c r="R74" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B75,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B75" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K75" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="L75" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="M75" s="6" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N75" s="6" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="O75" s="7" t="n">
+        <f aca="false">(N75-M75)*24</f>
+        <v>12</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q75" s="7" t="n">
+        <f aca="false">P75*O75</f>
+        <v>48</v>
+      </c>
+      <c r="R75" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="13" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B76,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B76" s="14" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H76" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I76" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="K76" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L76" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="M76" s="16" t="n">
+        <v>0.397222222222222</v>
+      </c>
+      <c r="N76" s="16" t="n">
+        <v>0.472222222222222</v>
+      </c>
+      <c r="O76" s="17" t="n">
+        <f aca="false">(N76-M76)*24</f>
+        <v>1.8</v>
+      </c>
+      <c r="P76" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q76" s="17" t="n">
+        <f aca="false">P76*O76</f>
+        <v>3.6</v>
+      </c>
+      <c r="R76" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B77,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B77" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C77" s="5"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L77" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M77" s="6" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N77" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="O77" s="7" t="n">
+        <f aca="false">(N77-M77)*24</f>
+        <v>8</v>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q77" s="7" t="n">
+        <f aca="false">P77*O77</f>
+        <v>88</v>
+      </c>
+      <c r="R77" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="8" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B78,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B78" s="9" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J78" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K78" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="L78" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="M78" s="11" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="N78" s="11" t="n">
+        <v>0.420833333333333</v>
+      </c>
+      <c r="O78" s="12" t="n">
+        <f aca="false">(N78-M78)*24</f>
+        <v>0.1</v>
+      </c>
+      <c r="P78" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q78" s="12" t="n">
+        <f aca="false">P78*O78</f>
+        <v>0.3</v>
+      </c>
+      <c r="R78" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B79,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B79" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K79" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="L79" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="M79" s="6" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N79" s="6" t="n">
+        <v>0.395833333333333</v>
+      </c>
+      <c r="O79" s="7" t="n">
+        <f aca="false">(N79-M79)*24</f>
+        <v>1.5</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q79" s="7" t="n">
+        <f aca="false">P79*O79</f>
+        <v>3</v>
+      </c>
+      <c r="R79" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B80,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K80" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="L80" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="M80" s="6" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N80" s="6" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O80" s="7" t="n">
+        <f aca="false">(N80-M80)*24</f>
+        <v>7</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q80" s="7" t="n">
+        <f aca="false">P80*O80</f>
         <v>14</v>
       </c>
-      <c r="R57" s="3" t="s">
+      <c r="R80" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P58" s="18" t="s">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P81" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="Q58" s="19" t="n">
-        <f aca="false">SUM(Q3:Q57)</f>
-        <v>1840.33333333333</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="20" t="s">
+      <c r="Q81" s="19" t="n">
+        <f aca="false">SUM(Q3:Q80)</f>
+        <v>3344.33333333333</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="20" t="s">
         <v>132</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R57"/>
+  <autoFilter ref="A2:R80"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4452,7 +5625,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -4519,39 +5692,39 @@
         <v>W41</v>
       </c>
       <c r="D4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A4,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>46</v>
       </c>
       <c r="E4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A4,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
         <v>120</v>
       </c>
       <c r="F4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A4,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0</v>
       </c>
       <c r="G4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A4,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0</v>
       </c>
       <c r="H4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A4,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A4,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A4,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>0</v>
       </c>
       <c r="K4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A4,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L4" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A4,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A4,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M4" s="24" t="n">
@@ -4571,39 +5744,39 @@
         <v>W41</v>
       </c>
       <c r="D5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A5,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>55</v>
       </c>
       <c r="E5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A5,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
         <v>120</v>
       </c>
       <c r="F5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A5,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0</v>
       </c>
       <c r="G5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A5,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0</v>
       </c>
       <c r="H5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A5,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A5,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A5,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>0</v>
       </c>
       <c r="K5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A5,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L5" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A5,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A5,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M5" s="24" t="n">
@@ -4623,39 +5796,39 @@
         <v>W41</v>
       </c>
       <c r="D6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A6,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A6,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
         <v>112</v>
       </c>
       <c r="F6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A6,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0</v>
       </c>
       <c r="G6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A6,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0</v>
       </c>
       <c r="H6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A6,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A6,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A6,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>0</v>
       </c>
       <c r="K6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A6,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L6" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A6,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A6,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M6" s="24" t="n">
@@ -4675,39 +5848,39 @@
         <v>W41</v>
       </c>
       <c r="D7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A7,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A7,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
         <v>104</v>
       </c>
       <c r="F7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A7,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0.2</v>
       </c>
       <c r="G7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A7,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0</v>
       </c>
       <c r="H7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A7,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A7,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A7,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>0</v>
       </c>
       <c r="K7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A7,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L7" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A7,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A7,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M7" s="24" t="n">
@@ -4727,39 +5900,39 @@
         <v>W41</v>
       </c>
       <c r="D8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A8,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A8,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
         <v>132</v>
       </c>
       <c r="F8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A8,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0.6</v>
       </c>
       <c r="G8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A8,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0</v>
       </c>
       <c r="H8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A8,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A8,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A8,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>0</v>
       </c>
       <c r="K8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A8,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L8" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A8,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A8,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M8" s="24" t="n">
@@ -4779,39 +5952,39 @@
         <v>W41</v>
       </c>
       <c r="D9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A9,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A9,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
         <v>116</v>
       </c>
       <c r="F9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A9,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0</v>
       </c>
       <c r="G9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A9,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>3</v>
       </c>
       <c r="H9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A9,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A9,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A9,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>0</v>
       </c>
       <c r="K9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A9,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L9" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A9,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A9,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M9" s="24" t="n">
@@ -4831,39 +6004,39 @@
         <v>W41</v>
       </c>
       <c r="D10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A10,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A10,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
         <v>72</v>
       </c>
       <c r="F10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A10,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0</v>
       </c>
       <c r="G10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A10,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0</v>
       </c>
       <c r="H10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A10,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A10,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A10,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>0</v>
       </c>
       <c r="K10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A10,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L10" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A10,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A10,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M10" s="24" t="n">
@@ -4883,44 +6056,44 @@
         <v>W42</v>
       </c>
       <c r="D11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A11,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A11,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
+        <v>132</v>
       </c>
       <c r="F11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A11,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0</v>
       </c>
       <c r="G11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A11,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0</v>
       </c>
       <c r="H11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A11,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A11,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>18</v>
       </c>
       <c r="J11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A11,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>144</v>
       </c>
       <c r="K11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A11,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L11" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A11,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A11,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M11" s="24" t="n">
         <f aca="false">SUM(D11:L11)</f>
-        <v>162</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4935,44 +6108,44 @@
         <v>W42</v>
       </c>
       <c r="D12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A12,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A12,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
+        <v>140</v>
       </c>
       <c r="F12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A12,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0</v>
       </c>
       <c r="G12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A12,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0</v>
       </c>
       <c r="H12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A12,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A12,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>4.5</v>
       </c>
       <c r="J12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A12,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>144</v>
       </c>
       <c r="K12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A12,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L12" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A12,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A12,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M12" s="24" t="n">
         <f aca="false">SUM(D12:L12)</f>
-        <v>148.5</v>
+        <v>288.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4987,44 +6160,44 @@
         <v>W42</v>
       </c>
       <c r="D13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A13,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A13,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
+        <v>132</v>
       </c>
       <c r="F13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A13,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0</v>
       </c>
       <c r="G13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A13,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0</v>
       </c>
       <c r="H13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A13,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>2</v>
       </c>
       <c r="I13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A13,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A13,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>144</v>
       </c>
       <c r="K13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A13,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L13" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A13,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A13,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M13" s="24" t="n">
         <f aca="false">SUM(D13:L13)</f>
-        <v>146</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5039,44 +6212,44 @@
         <v>W42</v>
       </c>
       <c r="D14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A14,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A14,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
+        <v>132</v>
       </c>
       <c r="F14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A14,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0</v>
       </c>
       <c r="G14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A14,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0.333333333333333</v>
       </c>
       <c r="H14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A14,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A14,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A14,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>144</v>
       </c>
       <c r="K14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A14,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L14" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A14,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A14,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>32</v>
       </c>
       <c r="M14" s="24" t="n">
         <f aca="false">SUM(D14:L14)</f>
-        <v>176.333333333333</v>
+        <v>308.333333333333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5091,44 +6264,44 @@
         <v>W42</v>
       </c>
       <c r="D15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A15,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A15,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
+        <v>116</v>
       </c>
       <c r="F15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A15,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0.75</v>
       </c>
       <c r="G15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A15,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0</v>
       </c>
       <c r="H15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A15,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A15,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A15,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>144</v>
       </c>
       <c r="K15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A15,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>9</v>
       </c>
       <c r="L15" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A15,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A15,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M15" s="24" t="n">
         <f aca="false">SUM(D15:L15)</f>
-        <v>153.75</v>
+        <v>269.75</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5143,44 +6316,44 @@
         <v>W42</v>
       </c>
       <c r="D16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A16,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A16,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
+        <v>128</v>
       </c>
       <c r="F16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A16,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0.2</v>
       </c>
       <c r="G16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A16,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0</v>
       </c>
       <c r="H16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A16,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A16,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A16,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>96</v>
       </c>
       <c r="K16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A16,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L16" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A16,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A16,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M16" s="24" t="n">
         <f aca="false">SUM(D16:L16)</f>
-        <v>96.2</v>
+        <v>224.2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5195,44 +6368,44 @@
         <v>W43</v>
       </c>
       <c r="D17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A17,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A17,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
+        <v>136</v>
       </c>
       <c r="F17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A17,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0.35</v>
       </c>
       <c r="G17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A17,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0</v>
       </c>
       <c r="H17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A17,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A17,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A17,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>0</v>
       </c>
       <c r="K17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A17,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L17" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A17,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A17,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M17" s="24" t="n">
         <f aca="false">SUM(D17:L17)</f>
-        <v>0.35</v>
+        <v>136.35</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5247,287 +6420,339 @@
         <v>W43</v>
       </c>
       <c r="D18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A18,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A18,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
+        <v>136</v>
       </c>
       <c r="F18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A18,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
         <v>0.4</v>
       </c>
       <c r="G18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A18,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>4</v>
       </c>
       <c r="H18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A18,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A18,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A18,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>0</v>
       </c>
       <c r="K18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A18,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L18" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A18,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A18,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M18" s="24" t="n">
         <f aca="false">SUM(D18:L18)</f>
-        <v>4.4</v>
+        <v>140.4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C19" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A19,21)</f>
         <v>W43</v>
       </c>
       <c r="D19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A19,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A19,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
+        <v>128</v>
       </c>
       <c r="F19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
-        <v>3.1</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A19,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
+        <v>0</v>
       </c>
       <c r="G19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A19,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
         <v>0</v>
       </c>
       <c r="H19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A19,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
         <v>0</v>
       </c>
       <c r="I19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A19,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A19,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>0</v>
       </c>
       <c r="K19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A19,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L19" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A19,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A19,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M19" s="24" t="n">
         <f aca="false">SUM(D19:L19)</f>
-        <v>3.1</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A20,21)</f>
         <v>W43</v>
       </c>
       <c r="D20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A20,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A20,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
+        <v>108</v>
       </c>
       <c r="F20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A20,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
+        <v>3.1</v>
       </c>
       <c r="G20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
-        <v>48</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A20,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
+        <v>0</v>
       </c>
       <c r="H20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
-        <v>3.6</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A20,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
+        <v>0</v>
       </c>
       <c r="I20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A20,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A20,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>0</v>
       </c>
       <c r="K20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A20,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L20" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A20,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A20,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M20" s="24" t="n">
         <f aca="false">SUM(D20:L20)</f>
-        <v>51.6</v>
+        <v>111.1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="str">
         <f aca="false">"W"&amp;WEEKNUM(A21,21)</f>
         <v>W43</v>
       </c>
       <c r="D21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,D$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A21,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
         <v>0</v>
       </c>
       <c r="E21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,E$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A21,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
+        <v>128</v>
       </c>
       <c r="F21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,F$3)</f>
-        <v>0.3</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A21,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
+        <v>0</v>
       </c>
       <c r="G21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,G$3)</f>
-        <v>17</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A21,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
+        <v>48</v>
       </c>
       <c r="H21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,H$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A21,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
+        <v>3.6</v>
       </c>
       <c r="I21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,I$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A21,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
         <v>0</v>
       </c>
       <c r="J21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,J$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A21,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
         <v>0</v>
       </c>
       <c r="K21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,K$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A21,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
         <v>0</v>
       </c>
       <c r="L21" s="23" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$B$3:$B$57,$A21,'S32 5-10 đến 24-10'!$R$3:$R$57,L$3)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A21,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
         <v>0</v>
       </c>
       <c r="M21" s="24" t="n">
         <f aca="false">SUM(D21:L21)</f>
-        <v>17.3</v>
+        <v>179.6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="22" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="3" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(A22,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="D22" s="23" t="n">
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A22,'S32 5-10 đến 24-10'!$R$3:$R$80,D$3)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="23" t="n">
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A22,'S32 5-10 đến 24-10'!$R$3:$R$80,E$3)</f>
+        <v>88</v>
+      </c>
+      <c r="F22" s="23" t="n">
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A22,'S32 5-10 đến 24-10'!$R$3:$R$80,F$3)</f>
+        <v>0.3</v>
+      </c>
+      <c r="G22" s="23" t="n">
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A22,'S32 5-10 đến 24-10'!$R$3:$R$80,G$3)</f>
+        <v>17</v>
+      </c>
+      <c r="H22" s="23" t="n">
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A22,'S32 5-10 đến 24-10'!$R$3:$R$80,H$3)</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="23" t="n">
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A22,'S32 5-10 đến 24-10'!$R$3:$R$80,I$3)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="23" t="n">
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A22,'S32 5-10 đến 24-10'!$R$3:$R$80,J$3)</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="23" t="n">
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A22,'S32 5-10 đến 24-10'!$R$3:$R$80,K$3)</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="23" t="n">
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$B$3:$B$80,$A22,'S32 5-10 đến 24-10'!$R$3:$R$80,L$3)</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="24" t="n">
+        <f aca="false">SUM(D22:L22)</f>
+        <v>105.3</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="24" t="n">
-        <f aca="false">SUM(D4:D21)</f>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="24" t="n">
+        <f aca="false">SUM(D4:D22)</f>
         <v>101</v>
       </c>
-      <c r="E22" s="24" t="n">
-        <f aca="false">SUM(E4:E21)</f>
-        <v>776</v>
-      </c>
-      <c r="F22" s="24" t="n">
-        <f aca="false">SUM(F4:F21)</f>
+      <c r="E23" s="24" t="n">
+        <f aca="false">SUM(E4:E22)</f>
+        <v>2280</v>
+      </c>
+      <c r="F23" s="24" t="n">
+        <f aca="false">SUM(F4:F22)</f>
         <v>5.9</v>
       </c>
-      <c r="G22" s="24" t="n">
-        <f aca="false">SUM(G4:G21)</f>
+      <c r="G23" s="24" t="n">
+        <f aca="false">SUM(G4:G22)</f>
         <v>72.3333333333333</v>
       </c>
-      <c r="H22" s="24" t="n">
-        <f aca="false">SUM(H4:H21)</f>
+      <c r="H23" s="24" t="n">
+        <f aca="false">SUM(H4:H22)</f>
         <v>5.6</v>
       </c>
-      <c r="I22" s="24" t="n">
-        <f aca="false">SUM(I4:I21)</f>
+      <c r="I23" s="24" t="n">
+        <f aca="false">SUM(I4:I22)</f>
         <v>22.5</v>
       </c>
-      <c r="J22" s="24" t="n">
-        <f aca="false">SUM(J4:J21)</f>
+      <c r="J23" s="24" t="n">
+        <f aca="false">SUM(J4:J22)</f>
         <v>816</v>
       </c>
-      <c r="K22" s="24" t="n">
-        <f aca="false">SUM(K4:K21)</f>
+      <c r="K23" s="24" t="n">
+        <f aca="false">SUM(K4:K22)</f>
         <v>9</v>
       </c>
-      <c r="L22" s="24" t="n">
-        <f aca="false">SUM(L4:L21)</f>
+      <c r="L23" s="24" t="n">
+        <f aca="false">SUM(L4:L22)</f>
         <v>32</v>
       </c>
-      <c r="M22" s="24" t="n">
-        <f aca="false">SUM(M4:M21)</f>
-        <v>1840.33333333333</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="s">
+      <c r="M23" s="24" t="n">
+        <f aca="false">SUM(M4:M22)</f>
+        <v>3344.33333333333</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>146</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="B26" s="27" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$A$3:$A$57,A26)</f>
-        <v>880.8</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B27" s="27" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$A$3:$A$57,A27)</f>
-        <v>882.783333333333</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$A$3:$A$80,A27)</f>
+        <v>880.8</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" s="27" t="n">
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$A$3:$A$80,A28)</f>
+        <v>1662.78333333333</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="B28" s="27" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$A$3:$A$57,A28)</f>
-        <v>76.75</v>
+      <c r="B29" s="27" t="n">
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$A$3:$A$80,A29)</f>
+        <v>800.75</v>
       </c>
     </row>
   </sheetData>
@@ -5546,7 +6771,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -6422,7 +7647,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="n">
         <v>46307</v>
       </c>
@@ -6430,33 +7655,33 @@
         <v>21</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="D25" s="30" t="s">
         <v>20</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F25" s="32" t="n">
         <v>0.3125</v>
       </c>
       <c r="G25" s="32" t="n">
-        <v>0.625</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="H25" s="30" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I25" s="33"/>
       <c r="J25" s="34"/>
       <c r="K25" s="35" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="L25" s="34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="29" t="n">
         <v>46307</v>
       </c>
@@ -6464,37 +7689,33 @@
         <v>21</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="D26" s="30" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F26" s="32" t="n">
-        <v>0.395833333333333</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="G26" s="32" t="n">
-        <v>0.833333333333333</v>
+        <v>0.8125</v>
       </c>
       <c r="H26" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="J26" s="34" t="n">
-        <v>2522</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I26" s="33"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="35" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="L26" s="34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="n">
         <v>46307</v>
       </c>
@@ -6502,50 +7723,50 @@
         <v>21</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="F27" s="32" t="n">
         <v>0.3125</v>
       </c>
       <c r="G27" s="32" t="n">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
       <c r="H27" s="30" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I27" s="33"/>
       <c r="J27" s="34"/>
       <c r="K27" s="35" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L27" s="34" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B28" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D28" s="30" t="s">
         <v>20</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F28" s="32" t="n">
-        <v>0.645833333333333</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="G28" s="32" t="n">
         <v>0.833333333333333</v>
@@ -6554,13 +7775,13 @@
         <v>1</v>
       </c>
       <c r="I28" s="33" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J28" s="34" t="n">
-        <v>9</v>
+        <v>2522</v>
       </c>
       <c r="K28" s="35" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L28" s="34" t="s">
         <v>65</v>
@@ -6568,7 +7789,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B29" s="30" t="s">
         <v>21</v>
@@ -6600,119 +7821,115 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B30" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="E30" s="30" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="F30" s="32" t="n">
-        <v>0.375</v>
+        <v>0.3125</v>
       </c>
       <c r="G30" s="32" t="n">
-        <v>0.416666666666667</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="H30" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="J30" s="34" t="n">
-        <v>100</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="I30" s="33"/>
+      <c r="J30" s="34"/>
       <c r="K30" s="35" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="L30" s="34" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B31" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="E31" s="30" t="s">
         <v>30</v>
       </c>
       <c r="F31" s="32" t="n">
-        <v>0.3125</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="G31" s="32" t="n">
         <v>0.8125</v>
       </c>
       <c r="H31" s="30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I31" s="33"/>
       <c r="J31" s="34"/>
       <c r="K31" s="35" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="L31" s="34" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="29" t="n">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="B32" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D32" s="30" t="s">
         <v>20</v>
       </c>
       <c r="E32" s="30" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="F32" s="32" t="n">
-        <v>0.333333333333333</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="G32" s="32" t="n">
-        <v>0.347222222222222</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="H32" s="30" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="33" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="J32" s="34" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K32" s="35" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="L32" s="34" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="n">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="B33" s="30" t="s">
         <v>21</v>
@@ -6745,122 +7962,114 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="40" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B34" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="D34" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E34" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="F34" s="43" t="n">
-        <v>0.291666666666667</v>
-      </c>
-      <c r="G34" s="43" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="H34" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="I34" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="J34" s="34" t="n">
-        <v>734</v>
-      </c>
+      <c r="A34" s="29" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" s="32" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G34" s="32" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="H34" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="I34" s="33"/>
+      <c r="J34" s="34"/>
       <c r="K34" s="35" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="L34" s="34" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="36" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B35" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="F35" s="39" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="G35" s="39" t="n">
-        <v>0.336805555555556</v>
-      </c>
-      <c r="H35" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="I35" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="J35" s="34" t="n">
-        <v>14</v>
-      </c>
+      <c r="A35" s="29" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35" s="32" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="G35" s="32" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H35" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="I35" s="33"/>
+      <c r="J35" s="34"/>
       <c r="K35" s="35" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="L35" s="34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="36" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B36" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="F36" s="39" t="n">
-        <v>0.336805555555556</v>
-      </c>
-      <c r="G36" s="39" t="n">
-        <v>0.34375</v>
-      </c>
-      <c r="H36" s="37" t="n">
-        <v>3</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="29" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="32" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G36" s="32" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="H36" s="30" t="n">
+        <v>2</v>
       </c>
       <c r="I36" s="33" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="J36" s="34" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="K36" s="35" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="L36" s="34" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="29" t="n">
-        <v>46311</v>
+        <v>46309</v>
       </c>
       <c r="B37" s="30" t="s">
         <v>21</v>
@@ -6894,271 +8103,259 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="29" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B38" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="E38" s="30" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F38" s="32" t="n">
-        <v>0.333333333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="G38" s="32" t="n">
-        <v>0.5</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="H38" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="33" t="s">
-        <v>91</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="I38" s="33"/>
       <c r="J38" s="34"/>
       <c r="K38" s="35" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="L38" s="34" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="40" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B39" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" s="42" t="s">
-        <v>92</v>
-      </c>
-      <c r="D39" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E39" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="F39" s="43" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G39" s="43" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="H39" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" s="33" t="s">
-        <v>95</v>
-      </c>
+      <c r="A39" s="29" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="32" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="G39" s="32" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H39" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="I39" s="33"/>
       <c r="J39" s="34"/>
       <c r="K39" s="35" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="L39" s="34" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="29" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B40" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D40" s="30" t="s">
         <v>20</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="F40" s="32" t="n">
-        <v>0.541666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="G40" s="32" t="n">
-        <v>0.544444444444444</v>
+        <v>0.347222222222222</v>
       </c>
       <c r="H40" s="30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I40" s="33" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="J40" s="34" t="n">
         <v>4</v>
       </c>
       <c r="K40" s="35" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="L40" s="34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="40" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B41" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41" s="42" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="29" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B41" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="41" t="s">
+      <c r="D41" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E41" s="41" t="s">
+      <c r="E41" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="F41" s="43" t="n">
+      <c r="F41" s="32" t="n">
         <v>0.3125</v>
       </c>
-      <c r="G41" s="43" t="n">
-        <v>0.645833333333333</v>
-      </c>
-      <c r="H41" s="41" t="n">
+      <c r="G41" s="32" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H41" s="30" t="n">
         <v>12</v>
       </c>
       <c r="I41" s="33"/>
       <c r="J41" s="34"/>
       <c r="K41" s="35" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="L41" s="34" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="29" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B42" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C42" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F42" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G42" s="32" t="n">
-        <v>0.751388888888889</v>
-      </c>
-      <c r="H42" s="30" t="n">
-        <v>3</v>
+      <c r="A42" s="40" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B42" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E42" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="F42" s="43" t="n">
+        <v>0.291666666666667</v>
+      </c>
+      <c r="G42" s="43" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H42" s="41" t="n">
+        <v>4</v>
       </c>
       <c r="I42" s="33" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="J42" s="34" t="n">
-        <v>1</v>
+        <v>734</v>
       </c>
       <c r="K42" s="35" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="L42" s="34" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="29" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="B43" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="D43" s="30" t="s">
         <v>20</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F43" s="32" t="n">
-        <v>0.751388888888889</v>
+        <v>0.3125</v>
       </c>
       <c r="G43" s="32" t="n">
-        <v>0.752777777777778</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="H43" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="I43" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="J43" s="34" t="n">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I43" s="33"/>
+      <c r="J43" s="34"/>
       <c r="K43" s="35" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="L43" s="34" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="29" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="B44" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D44" s="30" t="s">
         <v>20</v>
       </c>
       <c r="E44" s="30" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F44" s="32" t="n">
-        <v>0.752777777777778</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="G44" s="32" t="n">
-        <v>0.754861111111111</v>
+        <v>0.8125</v>
       </c>
       <c r="H44" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="I44" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="J44" s="34" t="n">
-        <v>3</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I44" s="33"/>
+      <c r="J44" s="34"/>
       <c r="K44" s="35" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="L44" s="34" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="36" t="n">
-        <v>46315</v>
+        <v>46311</v>
       </c>
       <c r="B45" s="37" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D45" s="37" t="s">
         <v>20</v>
@@ -7167,19 +8364,19 @@
         <v>87</v>
       </c>
       <c r="F45" s="39" t="n">
-        <v>0.756944444444444</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="G45" s="39" t="n">
-        <v>0.760416666666667</v>
+        <v>0.336805555555556</v>
       </c>
       <c r="H45" s="37" t="n">
         <v>3</v>
       </c>
       <c r="I45" s="33" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="J45" s="34" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K45" s="35" t="s">
         <v>89</v>
@@ -7190,13 +8387,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="36" t="n">
-        <v>46315</v>
+        <v>46311</v>
       </c>
       <c r="B46" s="37" t="s">
         <v>21</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D46" s="37" t="s">
         <v>20</v>
@@ -7205,19 +8402,19 @@
         <v>87</v>
       </c>
       <c r="F46" s="39" t="n">
-        <v>0.760416666666667</v>
+        <v>0.336805555555556</v>
       </c>
       <c r="G46" s="39" t="n">
-        <v>0.7625</v>
+        <v>0.34375</v>
       </c>
       <c r="H46" s="37" t="n">
         <v>3</v>
       </c>
       <c r="I46" s="33" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="J46" s="34" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K46" s="35" t="s">
         <v>89</v>
@@ -7228,127 +8425,119 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="29" t="n">
-        <v>46315</v>
+        <v>46311</v>
       </c>
       <c r="B47" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="E47" s="30" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="F47" s="32" t="n">
-        <v>0.375</v>
+        <v>0.3125</v>
       </c>
       <c r="G47" s="32" t="n">
-        <v>0.409722222222222</v>
+        <v>0.8125</v>
       </c>
       <c r="H47" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="I47" s="33"/>
+      <c r="J47" s="34"/>
+      <c r="K47" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="L47" s="34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="29" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B48" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="F48" s="32" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="G48" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H48" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="I47" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="J47" s="34" t="n">
-        <v>30</v>
-      </c>
-      <c r="K47" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="L47" s="34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="36" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B48" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C48" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="F48" s="39" t="n">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="G48" s="39" t="n">
-        <v>0.46875</v>
-      </c>
-      <c r="H48" s="37" t="n">
-        <v>2</v>
-      </c>
       <c r="I48" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="J48" s="34" t="n">
-        <v>2</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="J48" s="34"/>
       <c r="K48" s="35" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="L48" s="34" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="29" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B49" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="D49" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="F49" s="32" t="n">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="G49" s="32" t="n">
-        <v>0.444444444444444</v>
-      </c>
-      <c r="H49" s="30" t="n">
+      <c r="A49" s="40" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B49" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" s="43" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G49" s="43" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="H49" s="41" t="n">
         <v>1</v>
       </c>
       <c r="I49" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="J49" s="34" t="n">
-        <v>30</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="J49" s="34"/>
       <c r="K49" s="35" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="L49" s="34" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="29" t="n">
-        <v>46317</v>
+        <v>46312</v>
       </c>
       <c r="B50" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="31" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D50" s="30" t="s">
         <v>20</v>
@@ -7357,255 +8546,1073 @@
         <v>30</v>
       </c>
       <c r="F50" s="32" t="n">
-        <v>0.333333333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="G50" s="32" t="n">
-        <v>0.334722222222222</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="H50" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="I50" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="J50" s="34" t="n">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="I50" s="33"/>
+      <c r="J50" s="34"/>
       <c r="K50" s="35" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="L50" s="34" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="29" t="n">
-        <v>46317</v>
+        <v>46312</v>
       </c>
       <c r="B51" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="31" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D51" s="30" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="30" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="F51" s="32" t="n">
-        <v>0.375</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="G51" s="32" t="n">
-        <v>0.416666666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="H51" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="I51" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="J51" s="34" t="n">
-        <v>20</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="I51" s="33"/>
+      <c r="J51" s="34"/>
       <c r="K51" s="35" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="L51" s="34" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="29" t="n">
-        <v>46318</v>
+        <v>46312</v>
       </c>
       <c r="B52" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="31" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="D52" s="30" t="s">
         <v>20</v>
       </c>
       <c r="E52" s="30" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="F52" s="32" t="n">
-        <v>0.333333333333333</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="G52" s="32" t="n">
-        <v>0.833333333333333</v>
+        <v>0.544444444444444</v>
       </c>
       <c r="H52" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I52" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="J52" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="I52" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="J52" s="34" t="n">
-        <v>30</v>
-      </c>
       <c r="K52" s="35" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="L52" s="34" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="40" t="n">
-        <v>46318</v>
+        <v>46312</v>
       </c>
       <c r="B53" s="41" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="42" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="D53" s="41" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E53" s="41" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="F53" s="43" t="n">
-        <v>0.397222222222222</v>
+        <v>0.3125</v>
       </c>
       <c r="G53" s="43" t="n">
-        <v>0.472222222222222</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="H53" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="J53" s="34" t="n">
-        <v>65</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="I53" s="33"/>
+      <c r="J53" s="34"/>
       <c r="K53" s="35" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="L53" s="34" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="36" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B54" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="D54" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="E54" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="F54" s="39" t="n">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="G54" s="39" t="n">
-        <v>0.420833333333333</v>
-      </c>
-      <c r="H54" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="I54" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="J54" s="34" t="n">
-        <v>50</v>
-      </c>
+      <c r="A54" s="29" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B54" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F54" s="32" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G54" s="32" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="H54" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="I54" s="33"/>
+      <c r="J54" s="34"/>
       <c r="K54" s="35" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="L54" s="34" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="29" t="n">
-        <v>46319</v>
+        <v>46314</v>
       </c>
       <c r="B55" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C55" s="31" t="s">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="D55" s="30" t="s">
         <v>20</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="F55" s="32" t="n">
-        <v>0.333333333333333</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="G55" s="32" t="n">
-        <v>0.395833333333333</v>
+        <v>0.8125</v>
       </c>
       <c r="H55" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="I55" s="33" t="s">
-        <v>127</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I55" s="33"/>
       <c r="J55" s="34"/>
       <c r="K55" s="35" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="L55" s="34" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="29" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B56" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D56" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="F56" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G56" s="32" t="n">
+        <v>0.751388888888889</v>
+      </c>
+      <c r="H56" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="J56" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="L56" s="34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="29" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B57" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="D57" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="F57" s="32" t="n">
+        <v>0.751388888888889</v>
+      </c>
+      <c r="G57" s="32" t="n">
+        <v>0.752777777777778</v>
+      </c>
+      <c r="H57" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="J57" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="L57" s="34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="29" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B58" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="F58" s="32" t="n">
+        <v>0.752777777777778</v>
+      </c>
+      <c r="G58" s="32" t="n">
+        <v>0.754861111111111</v>
+      </c>
+      <c r="H58" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="J58" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="L58" s="34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="29" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B59" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D59" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F59" s="32" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G59" s="32" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="H59" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="I59" s="33"/>
+      <c r="J59" s="34"/>
+      <c r="K59" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L59" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="29" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B60" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D60" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F60" s="32" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="G60" s="32" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H60" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="I60" s="33"/>
+      <c r="J60" s="34"/>
+      <c r="K60" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="L60" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="36" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B61" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D61" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="F61" s="39" t="n">
+        <v>0.756944444444444</v>
+      </c>
+      <c r="G61" s="39" t="n">
+        <v>0.760416666666667</v>
+      </c>
+      <c r="H61" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I61" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="J61" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="K61" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="L61" s="34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="36" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B62" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C62" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D62" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="F62" s="39" t="n">
+        <v>0.760416666666667</v>
+      </c>
+      <c r="G62" s="39" t="n">
+        <v>0.7625</v>
+      </c>
+      <c r="H62" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I62" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="J62" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K62" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="L62" s="34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="29" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B63" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F63" s="32" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G63" s="32" t="n">
+        <v>0.409722222222222</v>
+      </c>
+      <c r="H63" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="J63" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="K63" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="L63" s="34" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="36" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B64" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="D64" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="F64" s="39" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="G64" s="39" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="H64" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="J64" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K64" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="L64" s="34" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="29" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D65" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F65" s="32" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="G65" s="32" t="n">
+        <v>0.444444444444444</v>
+      </c>
+      <c r="H65" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="J65" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="K65" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="L65" s="34" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="29" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F66" s="32" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="H66" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="I66" s="33"/>
+      <c r="J66" s="34"/>
+      <c r="K66" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L66" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="29" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B67" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C67" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D67" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F67" s="32" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H67" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="I67" s="33"/>
+      <c r="J67" s="34"/>
+      <c r="K67" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="L67" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="29" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B68" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C68" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D68" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="H68" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="I68" s="33"/>
+      <c r="J68" s="34"/>
+      <c r="K68" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L68" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="29" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B69" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D69" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H69" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="I69" s="33"/>
+      <c r="J69" s="34"/>
+      <c r="K69" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="L69" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="29" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B70" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D70" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E70" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>0.334722222222222</v>
+      </c>
+      <c r="H70" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="J70" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="L70" s="34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="29" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B71" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D71" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="H71" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I71" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="J71" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="K71" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="L71" s="34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="29" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B72" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C72" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D72" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="H72" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="I72" s="33"/>
+      <c r="J72" s="34"/>
+      <c r="K72" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L72" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="29" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C73" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H73" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="I73" s="33"/>
+      <c r="J73" s="34"/>
+      <c r="K73" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="L73" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="29" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B74" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C74" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D74" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="H74" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I74" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="J74" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="K74" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="L74" s="34" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="40" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B75" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C75" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="D75" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="E75" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="F75" s="43" t="n">
+        <v>0.397222222222222</v>
+      </c>
+      <c r="G75" s="43" t="n">
+        <v>0.472222222222222</v>
+      </c>
+      <c r="H75" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="J75" s="34" t="n">
+        <v>65</v>
+      </c>
+      <c r="K75" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="L75" s="34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="29" t="n">
         <v>46319</v>
       </c>
-      <c r="B56" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C56" s="31" t="s">
+      <c r="B76" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D76" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="H76" s="30" t="n">
+        <v>11</v>
+      </c>
+      <c r="I76" s="33"/>
+      <c r="J76" s="34"/>
+      <c r="K76" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L76" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="36" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B77" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C77" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="D77" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E77" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="F77" s="39" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="G77" s="39" t="n">
+        <v>0.420833333333333</v>
+      </c>
+      <c r="H77" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="J77" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="K77" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="L77" s="34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="29" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B78" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C78" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D78" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>0.395833333333333</v>
+      </c>
+      <c r="H78" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I78" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="J78" s="34"/>
+      <c r="K78" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="L78" s="34" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="29" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B79" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C79" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="D56" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E56" s="30" t="s">
+      <c r="D79" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="F56" s="32" t="n">
+      <c r="F79" s="32" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="G56" s="32" t="n">
+      <c r="G79" s="32" t="n">
         <v>0.625</v>
       </c>
-      <c r="H56" s="30" t="n">
+      <c r="H79" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="33" t="s">
+      <c r="I79" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="J56" s="34" t="n">
+      <c r="J79" s="34" t="n">
         <v>22</v>
       </c>
-      <c r="K56" s="35" t="s">
+      <c r="K79" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="L56" s="34" t="s">
+      <c r="L79" s="34" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="20" t="s">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="20" t="s">
         <v>160</v>
       </c>
     </row>
@@ -7665,7 +9672,7 @@
         <v>5.9</v>
       </c>
       <c r="C4" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A4)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$R$3:$R$80,A4)</f>
         <v>5.9</v>
       </c>
       <c r="D4" s="46" t="n">
@@ -7682,11 +9689,11 @@
         <v>33</v>
       </c>
       <c r="B5" s="45" t="n">
-        <v>776</v>
+        <v>2280</v>
       </c>
       <c r="C5" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A5)</f>
-        <v>776</v>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$R$3:$R$80,A5)</f>
+        <v>2280</v>
       </c>
       <c r="D5" s="46" t="n">
         <f aca="false">C5-B5</f>
@@ -7705,7 +9712,7 @@
         <v>22.5</v>
       </c>
       <c r="C6" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A6)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$R$3:$R$80,A6)</f>
         <v>22.5</v>
       </c>
       <c r="D6" s="46" t="n">
@@ -7725,7 +9732,7 @@
         <v>101</v>
       </c>
       <c r="C7" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A7)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$R$3:$R$80,A7)</f>
         <v>101</v>
       </c>
       <c r="D7" s="46" t="n">
@@ -7745,7 +9752,7 @@
         <v>72.3333</v>
       </c>
       <c r="C8" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A8)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$R$3:$R$80,A8)</f>
         <v>72.3333333333333</v>
       </c>
       <c r="D8" s="46" t="n">
@@ -7765,7 +9772,7 @@
         <v>5.8333</v>
       </c>
       <c r="C9" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A9)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$R$3:$R$80,A9)</f>
         <v>5.6</v>
       </c>
       <c r="D9" s="46" t="n">
@@ -7785,7 +9792,7 @@
         <v>816</v>
       </c>
       <c r="C10" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A10)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$R$3:$R$80,A10)</f>
         <v>816</v>
       </c>
       <c r="D10" s="46" t="n">
@@ -7805,7 +9812,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A11)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$R$3:$R$80,A11)</f>
         <v>9</v>
       </c>
       <c r="D11" s="46" t="n">
@@ -7825,7 +9832,7 @@
         <v>32</v>
       </c>
       <c r="C12" s="46" t="n">
-        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$57,'S32 5-10 đến 24-10'!$R$3:$R$57,A12)</f>
+        <f aca="false">SUMIFS('S32 5-10 đến 24-10'!$Q$3:$Q$80,'S32 5-10 đến 24-10'!$R$3:$R$80,A12)</f>
         <v>32</v>
       </c>
       <c r="D12" s="46" t="n">
@@ -7843,11 +9850,11 @@
       </c>
       <c r="B13" s="48" t="n">
         <f aca="false">SUM(B4:B12)</f>
-        <v>1840.5666</v>
+        <v>3344.5666</v>
       </c>
       <c r="C13" s="48" t="n">
         <f aca="false">SUM(C4:C12)</f>
-        <v>1840.33333333333</v>
+        <v>3344.33333333333</v>
       </c>
       <c r="D13" s="48" t="n">
         <f aca="false">SUM(D4:D12)</f>
@@ -8601,7 +10608,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="51" t="s">
         <v>213</v>
       </c>
@@ -8621,7 +10628,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="51" t="s">
         <v>217</v>
       </c>
